--- a/docs/lightml/REPOSITORY_COMPLETENESS_REPORT.xlsx
+++ b/docs/lightml/REPOSITORY_COMPLETENESS_REPORT.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F227"/>
+  <dimension ref="A1:I227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -494,6 +494,12 @@
           <t>Evidence Source</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Repository Completeness Summary</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -526,6 +532,16 @@
           <t>Filesystem</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Repository Completeness</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100.0% (All expected engineering artifacts, detection specifications, and contract corpus files are present in the filesystem)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -558,6 +574,16 @@
           <t>Filesystem</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Engineering Completeness</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>19.6% (11 Technically Mature profiles have completed individual JSON configurations. 45 Partially Usable profiles require individual JSON configurations to be completed in future engineering phases.)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -590,6 +616,16 @@
           <t>Filesystem</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Legal Completeness</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>19.6% (11 Technically Mature profiles have completed Legal Evidence packages. 45 Partially Usable profiles lack Legal Evidence packages and are marked Pending.)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -620,6 +656,16 @@
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Filesystem</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Production Readiness</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pending (Formal legal review and formal legal approval are pending for all 56 registered profiles. The repository is not approved for production release.)</t>
         </is>
       </c>
     </row>

--- a/docs/lightml/REPOSITORY_COMPLETENESS_REPORT.xlsx
+++ b/docs/lightml/REPOSITORY_COMPLETENESS_REPORT.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I227"/>
+  <dimension ref="A1:I230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,6 @@
           <t>Repository Completeness Summary</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -623,7 +622,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>19.6% (11 Technically Mature profiles have completed Legal Evidence packages. 45 Partially Usable profiles lack Legal Evidence packages and are marked Pending.)</t>
+          <t>19.6% (11 Technically Mature profiles have Repository-supported Legal Evidence Package Prepared. 45 Partially Usable profiles lack Legal Evidence packages and are marked Pending.)</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2399,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: employment_contract/normal_contract.md</t>
+          <t>Incomplete Profile Spec: construction_contract</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/employment_contract/normal_contract.md</t>
+          <t>docs/lightml/detection_specifications/construction_contract.md</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -2432,12 +2431,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: employment_contract/missing_mandatory_clause.md</t>
+          <t>Incomplete Profile Spec: insurance_contract</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/employment_contract/missing_mandatory_clause.md</t>
+          <t>docs/lightml/detection_specifications/insurance_contract.md</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -2464,12 +2463,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: employment_contract/risky_contract.md</t>
+          <t>Incomplete Profile Spec: it_services_contract</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/employment_contract/risky_contract.md</t>
+          <t>docs/lightml/detection_specifications/it_services_contract.md</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -2496,12 +2495,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: lease_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: employment_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/lease_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/employment_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -2528,12 +2527,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: lease_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: employment_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/lease_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/employment_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -2560,12 +2559,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: lease_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: employment_contract/risky_contract.md</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/lease_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/employment_contract/risky_contract.md</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -2592,12 +2591,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: software_license/normal_contract.md</t>
+          <t>Corpus Fixture: lease_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/software_license/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/lease_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -2624,12 +2623,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: software_license/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: lease_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/software_license/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/lease_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -2656,12 +2655,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: software_license/risky_contract.md</t>
+          <t>Corpus Fixture: lease_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/software_license/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/lease_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -2688,12 +2687,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: service_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: software_license/normal_contract.md</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/service_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/software_license/normal_contract.md</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -2720,12 +2719,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: service_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: software_license/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/service_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/software_license/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -2752,12 +2751,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: service_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: software_license/risky_contract.md</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/service_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/software_license/risky_contract.md</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -2784,12 +2783,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: consulting_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: service_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/consulting_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/service_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -2816,12 +2815,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: consulting_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: service_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/consulting_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/service_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -2848,12 +2847,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: consulting_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: service_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/consulting_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/service_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -2880,12 +2879,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: commercial_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: consulting_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/commercial_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/consulting_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -2912,12 +2911,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: commercial_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: consulting_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/commercial_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/consulting_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -2944,12 +2943,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: commercial_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: consulting_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/commercial_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/consulting_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -2976,12 +2975,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: non_disclosure_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: commercial_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/non_disclosure_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/commercial_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -3008,12 +3007,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: non_disclosure_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: commercial_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/non_disclosure_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/commercial_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -3040,12 +3039,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: non_disclosure_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: commercial_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/non_disclosure_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/commercial_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -3072,12 +3071,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: loan_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: non_disclosure_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/loan_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/non_disclosure_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -3104,12 +3103,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: loan_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: non_disclosure_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/loan_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/non_disclosure_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -3136,12 +3135,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: loan_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: non_disclosure_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/loan_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/non_disclosure_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -3168,12 +3167,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: partnership_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: loan_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/partnership_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/loan_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -3200,12 +3199,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: partnership_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: loan_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/partnership_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/loan_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -3232,12 +3231,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: partnership_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: loan_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/partnership_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/loan_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3264,12 +3263,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: purchase_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: partnership_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/purchase_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/partnership_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -3296,12 +3295,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: purchase_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: partnership_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/purchase_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/partnership_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -3328,12 +3327,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: purchase_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: partnership_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/purchase_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/partnership_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -3360,12 +3359,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: distribution_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: purchase_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/distribution_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/purchase_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -3392,12 +3391,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: distribution_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: purchase_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/distribution_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/purchase_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -3424,12 +3423,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: distribution_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: purchase_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/distribution_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/purchase_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -3456,12 +3455,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: franchise_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: distribution_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/franchise_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/distribution_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -3488,12 +3487,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: franchise_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: distribution_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/franchise_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/distribution_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3520,12 +3519,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: franchise_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: distribution_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/franchise_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/distribution_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -3552,12 +3551,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: supply_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: franchise_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/supply_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/franchise_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -3584,12 +3583,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: supply_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: franchise_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/supply_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/franchise_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -3616,12 +3615,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: supply_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: franchise_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/supply_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/franchise_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -3648,12 +3647,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: agency_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: supply_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/agency_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/supply_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -3680,12 +3679,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: agency_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: supply_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/agency_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/supply_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -3712,12 +3711,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: agency_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: supply_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/agency_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/supply_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -3744,12 +3743,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: shareholder_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: agency_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/shareholder_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/agency_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -3776,12 +3775,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: shareholder_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: agency_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/shareholder_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/agency_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -3808,12 +3807,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: shareholder_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: agency_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/shareholder_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/agency_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -3840,12 +3839,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: investment_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: shareholder_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/investment_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/shareholder_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -3872,12 +3871,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: investment_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: shareholder_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/investment_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/shareholder_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -3904,12 +3903,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: investment_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: shareholder_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/investment_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/shareholder_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -3936,12 +3935,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: construction_contract/normal_contract.md</t>
+          <t>Corpus Fixture: investment_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/construction_contract/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/investment_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -3968,12 +3967,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: construction_contract/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: investment_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/construction_contract/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/investment_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -4000,12 +3999,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: construction_contract/risky_contract.md</t>
+          <t>Corpus Fixture: investment_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/construction_contract/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/investment_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -4032,12 +4031,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: maintenance_contract/normal_contract.md</t>
+          <t>Corpus Fixture: construction_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/maintenance_contract/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/construction_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -4064,12 +4063,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: maintenance_contract/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: construction_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/maintenance_contract/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/construction_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -4096,12 +4095,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: maintenance_contract/risky_contract.md</t>
+          <t>Corpus Fixture: construction_contract/risky_contract.md</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/maintenance_contract/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/construction_contract/risky_contract.md</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -4128,12 +4127,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: it_services_contract/normal_contract.md</t>
+          <t>Corpus Fixture: maintenance_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/it_services_contract/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/maintenance_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -4160,12 +4159,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: it_services_contract/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: maintenance_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/it_services_contract/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/maintenance_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -4192,12 +4191,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: it_services_contract/risky_contract.md</t>
+          <t>Corpus Fixture: maintenance_contract/risky_contract.md</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/it_services_contract/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/maintenance_contract/risky_contract.md</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -4224,12 +4223,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: data_processing_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: it_services_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/data_processing_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/it_services_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -4256,12 +4255,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: data_processing_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: it_services_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/data_processing_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/it_services_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -4288,12 +4287,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: data_processing_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: it_services_contract/risky_contract.md</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/data_processing_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/it_services_contract/risky_contract.md</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -4320,12 +4319,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: intellectual_property_assignment/normal_contract.md</t>
+          <t>Corpus Fixture: data_processing_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/intellectual_property_assignment/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/data_processing_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -4352,12 +4351,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: intellectual_property_assignment/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: data_processing_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/intellectual_property_assignment/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/data_processing_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -4384,12 +4383,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: intellectual_property_assignment/risky_contract.md</t>
+          <t>Corpus Fixture: data_processing_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/intellectual_property_assignment/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/data_processing_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -4416,12 +4415,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: licensing_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: intellectual_property_assignment/normal_contract.md</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/licensing_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/intellectual_property_assignment/normal_contract.md</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -4448,12 +4447,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: licensing_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: intellectual_property_assignment/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/licensing_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/intellectual_property_assignment/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -4480,12 +4479,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: licensing_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: intellectual_property_assignment/risky_contract.md</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/licensing_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/intellectual_property_assignment/risky_contract.md</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -4512,12 +4511,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: joint_venture_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: licensing_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/joint_venture_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/licensing_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -4544,12 +4543,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: joint_venture_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: licensing_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/joint_venture_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/licensing_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -4576,12 +4575,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: joint_venture_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: licensing_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/joint_venture_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/licensing_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -4608,12 +4607,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: memorandum_of_understanding/normal_contract.md</t>
+          <t>Corpus Fixture: joint_venture_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/memorandum_of_understanding/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/joint_venture_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -4640,12 +4639,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: memorandum_of_understanding/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: joint_venture_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/memorandum_of_understanding/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/joint_venture_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -4672,12 +4671,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: memorandum_of_understanding/risky_contract.md</t>
+          <t>Corpus Fixture: joint_venture_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/memorandum_of_understanding/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/joint_venture_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -4704,12 +4703,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: subcontract_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: memorandum_of_understanding/normal_contract.md</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/subcontract_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/memorandum_of_understanding/normal_contract.md</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -4736,12 +4735,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: subcontract_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: memorandum_of_understanding/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/subcontract_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/memorandum_of_understanding/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -4768,12 +4767,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: subcontract_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: memorandum_of_understanding/risky_contract.md</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/subcontract_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/memorandum_of_understanding/risky_contract.md</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -4800,12 +4799,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: grant_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: subcontract_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/grant_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/subcontract_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -4832,12 +4831,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: grant_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: subcontract_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/grant_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/subcontract_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -4864,12 +4863,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: grant_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: subcontract_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/grant_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/subcontract_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -4896,12 +4895,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: settlement_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: grant_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/settlement_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/grant_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -4928,12 +4927,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: settlement_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: grant_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/settlement_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/grant_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -4960,12 +4959,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: settlement_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: grant_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/settlement_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/grant_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -4992,12 +4991,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: sponsorship_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: settlement_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/sponsorship_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/settlement_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -5024,12 +5023,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: sponsorship_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: settlement_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/sponsorship_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/settlement_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -5056,12 +5055,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: sponsorship_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: settlement_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/sponsorship_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/settlement_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -5088,12 +5087,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: event_contract/normal_contract.md</t>
+          <t>Corpus Fixture: sponsorship_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/event_contract/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/sponsorship_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -5120,12 +5119,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: event_contract/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: sponsorship_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/event_contract/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/sponsorship_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -5152,12 +5151,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: event_contract/risky_contract.md</t>
+          <t>Corpus Fixture: sponsorship_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/event_contract/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/sponsorship_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -5184,12 +5183,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: property_management_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: event_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/property_management_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/event_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -5216,12 +5215,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: property_management_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: event_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/property_management_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/event_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -5248,12 +5247,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: property_management_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: event_contract/risky_contract.md</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/property_management_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/event_contract/risky_contract.md</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -5280,12 +5279,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: insurance_contract/normal_contract.md</t>
+          <t>Corpus Fixture: property_management_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/insurance_contract/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/property_management_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -5312,12 +5311,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: insurance_contract/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: property_management_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/insurance_contract/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/property_management_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -5344,12 +5343,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: insurance_contract/risky_contract.md</t>
+          <t>Corpus Fixture: property_management_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/insurance_contract/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/property_management_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -5376,12 +5375,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: escrow_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: insurance_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/escrow_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/insurance_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -5408,12 +5407,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: escrow_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: insurance_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/escrow_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/insurance_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -5440,12 +5439,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: escrow_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: insurance_contract/risky_contract.md</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/escrow_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/insurance_contract/risky_contract.md</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -5472,12 +5471,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: outsourcing_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: escrow_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/outsourcing_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/escrow_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -5504,12 +5503,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: outsourcing_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: escrow_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/outsourcing_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/escrow_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -5536,12 +5535,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: outsourcing_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: escrow_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/outsourcing_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/escrow_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -5568,12 +5567,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: employment_termination_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: outsourcing_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/employment_termination_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/outsourcing_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -5600,12 +5599,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: employment_termination_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: outsourcing_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/employment_termination_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/outsourcing_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -5632,12 +5631,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: employment_termination_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: outsourcing_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/employment_termination_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/outsourcing_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -5664,12 +5663,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: sales_representative_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: employment_termination_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/sales_representative_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/employment_termination_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -5696,12 +5695,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: sales_representative_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: employment_termination_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/sales_representative_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/employment_termination_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -5728,12 +5727,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: sales_representative_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: employment_termination_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/sales_representative_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/employment_termination_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -5760,12 +5759,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: freelance_contract/normal_contract.md</t>
+          <t>Corpus Fixture: sales_representative_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/freelance_contract/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/sales_representative_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -5792,12 +5791,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: freelance_contract/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: sales_representative_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/freelance_contract/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/sales_representative_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -5824,12 +5823,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: freelance_contract/risky_contract.md</t>
+          <t>Corpus Fixture: sales_representative_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/freelance_contract/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/sales_representative_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -5856,12 +5855,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: internship_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: freelance_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/internship_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/freelance_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -5888,12 +5887,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: internship_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: freelance_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/internship_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/freelance_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -5920,12 +5919,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: internship_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: freelance_contract/risky_contract.md</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/internship_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/freelance_contract/risky_contract.md</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -5952,12 +5951,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: facilities_management_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: internship_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/facilities_management_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/internship_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -5984,12 +5983,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: facilities_management_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: internship_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/facilities_management_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/internship_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -6016,12 +6015,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: facilities_management_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: internship_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/facilities_management_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/internship_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -6048,12 +6047,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: logistics_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: facilities_management_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/logistics_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/facilities_management_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -6080,12 +6079,12 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: logistics_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: facilities_management_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/logistics_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/facilities_management_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -6112,12 +6111,12 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: logistics_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: facilities_management_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/logistics_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/facilities_management_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -6144,12 +6143,12 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: media_production_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: logistics_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/media_production_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/logistics_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -6176,12 +6175,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: media_production_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: logistics_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/media_production_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/logistics_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -6208,12 +6207,12 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: media_production_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: logistics_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/media_production_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/logistics_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -6240,12 +6239,12 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: advertising_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: media_production_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/advertising_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/media_production_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -6272,12 +6271,12 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: advertising_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: media_production_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/advertising_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/media_production_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -6304,12 +6303,12 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: advertising_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: media_production_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/advertising_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/media_production_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -6336,12 +6335,12 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: cooperation_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: advertising_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/cooperation_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/advertising_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -6368,12 +6367,12 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: cooperation_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: advertising_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/cooperation_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/advertising_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -6400,12 +6399,12 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: cooperation_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: advertising_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/cooperation_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/advertising_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -6432,12 +6431,12 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: export_import_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: cooperation_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/export_import_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/cooperation_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -6464,12 +6463,12 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: export_import_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: cooperation_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/export_import_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/cooperation_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -6496,12 +6495,12 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: export_import_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: cooperation_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/export_import_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/cooperation_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -6528,12 +6527,12 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: land_acquisition_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: export_import_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/land_acquisition_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/export_import_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -6560,12 +6559,12 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: land_acquisition_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: export_import_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/land_acquisition_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/export_import_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -6592,12 +6591,12 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: land_acquisition_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: export_import_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/land_acquisition_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/export_import_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -6624,12 +6623,12 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: hotel_management_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: land_acquisition_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/hotel_management_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/land_acquisition_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -6656,12 +6655,12 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: hotel_management_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: land_acquisition_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/hotel_management_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/land_acquisition_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -6688,12 +6687,12 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: hotel_management_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: land_acquisition_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/hotel_management_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/land_acquisition_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -6720,12 +6719,12 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: healthcare_services_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: hotel_management_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/healthcare_services_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/hotel_management_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -6752,12 +6751,12 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: healthcare_services_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: hotel_management_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/healthcare_services_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/hotel_management_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -6784,12 +6783,12 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: healthcare_services_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: hotel_management_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/healthcare_services_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/hotel_management_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -6816,12 +6815,12 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: education_services_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: healthcare_services_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/education_services_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/healthcare_services_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -6848,12 +6847,12 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: education_services_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: healthcare_services_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/education_services_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/healthcare_services_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
@@ -6880,12 +6879,12 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: education_services_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: healthcare_services_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/education_services_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/healthcare_services_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -6912,12 +6911,12 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: energy_supply_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: education_services_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/energy_supply_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/education_services_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -6944,12 +6943,12 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: energy_supply_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: education_services_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/energy_supply_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/education_services_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -6976,12 +6975,12 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: energy_supply_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: education_services_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/energy_supply_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/education_services_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -7008,12 +7007,12 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: mining_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: energy_supply_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/mining_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/energy_supply_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -7040,12 +7039,12 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: mining_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: energy_supply_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/mining_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/energy_supply_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
@@ -7072,12 +7071,12 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: mining_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: energy_supply_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/mining_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/energy_supply_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -7104,12 +7103,12 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: telecommunications_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: mining_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/telecommunications_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/mining_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
@@ -7136,12 +7135,12 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: telecommunications_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: mining_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/telecommunications_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/mining_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
@@ -7168,12 +7167,12 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: telecommunications_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: mining_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/telecommunications_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/mining_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
@@ -7200,12 +7199,12 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: banking_facility_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: telecommunications_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/banking_facility_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/telecommunications_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
@@ -7232,12 +7231,12 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: banking_facility_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: telecommunications_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/banking_facility_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/telecommunications_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
@@ -7264,12 +7263,12 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: banking_facility_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: telecommunications_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/banking_facility_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/telecommunications_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
@@ -7296,12 +7295,12 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: factoring_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: banking_facility_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/factoring_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/banking_facility_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
@@ -7328,12 +7327,12 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: factoring_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: banking_facility_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/factoring_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/banking_facility_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
@@ -7360,12 +7359,12 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: factoring_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: banking_facility_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/factoring_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/banking_facility_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
@@ -7392,12 +7391,12 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: storage_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: factoring_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/storage_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/factoring_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
@@ -7424,12 +7423,12 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: storage_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: factoring_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/storage_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/factoring_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
@@ -7456,12 +7455,12 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: storage_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: factoring_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/storage_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/factoring_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
@@ -7488,12 +7487,12 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: research_collaboration_agreement/normal_contract.md</t>
+          <t>Corpus Fixture: storage_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/research_collaboration_agreement/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/storage_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
@@ -7520,12 +7519,12 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: research_collaboration_agreement/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: storage_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/research_collaboration_agreement/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/storage_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
@@ -7552,12 +7551,12 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: research_collaboration_agreement/risky_contract.md</t>
+          <t>Corpus Fixture: storage_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/research_collaboration_agreement/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/storage_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
@@ -7584,12 +7583,12 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: government_procurement_contract/normal_contract.md</t>
+          <t>Corpus Fixture: research_collaboration_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/government_procurement_contract/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/research_collaboration_agreement/normal_contract.md</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
@@ -7616,12 +7615,12 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: government_procurement_contract/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: research_collaboration_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/government_procurement_contract/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/research_collaboration_agreement/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
@@ -7648,12 +7647,12 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: government_procurement_contract/risky_contract.md</t>
+          <t>Corpus Fixture: research_collaboration_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/government_procurement_contract/risky_contract.md</t>
+          <t>docs/lightml/contract_corpus/research_collaboration_agreement/risky_contract.md</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -7680,12 +7679,12 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: general_contract/normal_contract.md</t>
+          <t>Corpus Fixture: government_procurement_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/general_contract/normal_contract.md</t>
+          <t>docs/lightml/contract_corpus/government_procurement_contract/normal_contract.md</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
@@ -7712,12 +7711,12 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Corpus Fixture: general_contract/missing_mandatory_clause.md</t>
+          <t>Corpus Fixture: government_procurement_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/contract_corpus/general_contract/missing_mandatory_clause.md</t>
+          <t>docs/lightml/contract_corpus/government_procurement_contract/missing_mandatory_clause.md</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
@@ -7744,30 +7743,126 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
+          <t>Corpus Fixture: government_procurement_contract/risky_contract.md</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>docs/lightml/contract_corpus/government_procurement_contract/risky_contract.md</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Filesystem</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Corpus Fixture: general_contract/normal_contract.md</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>docs/lightml/contract_corpus/general_contract/normal_contract.md</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>Filesystem</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Corpus Fixture: general_contract/missing_mandatory_clause.md</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>docs/lightml/contract_corpus/general_contract/missing_mandatory_clause.md</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Filesystem</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
           <t>Corpus Fixture: general_contract/risky_contract.md</t>
         </is>
       </c>
-      <c r="B227" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
         <is>
           <t>docs/lightml/contract_corpus/general_contract/risky_contract.md</t>
         </is>
       </c>
-      <c r="C227" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D227" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>Filesystem</t>
         </is>
